--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105329</v>
+        <v>120105328</v>
       </c>
       <c r="B3" t="n">
         <v>90527</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747539</v>
+        <v>747488</v>
       </c>
       <c r="R3" t="n">
-        <v>7085459</v>
+        <v>7085512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105328</v>
+        <v>120105329</v>
       </c>
       <c r="B4" t="n">
         <v>90527</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747488</v>
+        <v>747539</v>
       </c>
       <c r="R4" t="n">
-        <v>7085512</v>
+        <v>7085459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105330</v>
+        <v>120105329</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747596</v>
+        <v>747539</v>
       </c>
       <c r="R2" t="n">
-        <v>7085326</v>
+        <v>7085459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105329</v>
+        <v>120105330</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747539</v>
+        <v>747596</v>
       </c>
       <c r="R4" t="n">
-        <v>7085459</v>
+        <v>7085326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105328</v>
+        <v>120105330</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747488</v>
+        <v>747596</v>
       </c>
       <c r="R3" t="n">
-        <v>7085512</v>
+        <v>7085326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105330</v>
+        <v>120105328</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747596</v>
+        <v>747488</v>
       </c>
       <c r="R4" t="n">
-        <v>7085326</v>
+        <v>7085512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105329</v>
+        <v>120105328</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747539</v>
+        <v>747488</v>
       </c>
       <c r="R2" t="n">
-        <v>7085459</v>
+        <v>7085512</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>120105330</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105328</v>
+        <v>120105329</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747488</v>
+        <v>747539</v>
       </c>
       <c r="R4" t="n">
-        <v>7085512</v>
+        <v>7085459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105328</v>
+        <v>120105329</v>
       </c>
       <c r="B2" t="n">
         <v>90545</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747488</v>
+        <v>747539</v>
       </c>
       <c r="R2" t="n">
-        <v>7085512</v>
+        <v>7085459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105329</v>
+        <v>120105328</v>
       </c>
       <c r="B4" t="n">
         <v>90545</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747539</v>
+        <v>747488</v>
       </c>
       <c r="R4" t="n">
-        <v>7085459</v>
+        <v>7085512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105330</v>
+        <v>120105328</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747596</v>
+        <v>747488</v>
       </c>
       <c r="R3" t="n">
-        <v>7085326</v>
+        <v>7085512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105328</v>
+        <v>120105330</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747488</v>
+        <v>747596</v>
       </c>
       <c r="R4" t="n">
-        <v>7085512</v>
+        <v>7085326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105329</v>
+        <v>120105330</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747539</v>
+        <v>747596</v>
       </c>
       <c r="R2" t="n">
-        <v>7085459</v>
+        <v>7085326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105328</v>
+        <v>120105329</v>
       </c>
       <c r="B3" t="n">
         <v>90545</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747488</v>
+        <v>747539</v>
       </c>
       <c r="R3" t="n">
-        <v>7085512</v>
+        <v>7085459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105330</v>
+        <v>120105328</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747596</v>
+        <v>747488</v>
       </c>
       <c r="R4" t="n">
-        <v>7085326</v>
+        <v>7085512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105330</v>
+        <v>120105329</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747596</v>
+        <v>747539</v>
       </c>
       <c r="R2" t="n">
-        <v>7085326</v>
+        <v>7085459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105329</v>
+        <v>120105330</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747539</v>
+        <v>747596</v>
       </c>
       <c r="R3" t="n">
-        <v>7085459</v>
+        <v>7085326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35612-2024 artfynd.xlsx
+++ b/artfynd/A 35612-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105329</v>
+        <v>120105328</v>
       </c>
       <c r="B2" t="n">
         <v>90545</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747539</v>
+        <v>747488</v>
       </c>
       <c r="R2" t="n">
-        <v>7085459</v>
+        <v>7085512</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Maja Östlund, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105328</v>
+        <v>120105329</v>
       </c>
       <c r="B4" t="n">
         <v>90545</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747488</v>
+        <v>747539</v>
       </c>
       <c r="R4" t="n">
-        <v>7085512</v>
+        <v>7085459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Åsa Stenman</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
